--- a/gis_survey_outputs/tables/survey_analysis_tables.xlsx
+++ b/gis_survey_outputs/tables/survey_analysis_tables.xlsx
@@ -28,8 +28,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -100,7 +100,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1396,10 +1397,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>45810.71180555555</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>45810.71736111111</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -1681,10 +1682,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>45810.64097222222</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>45810.65208333333</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1950,10 +1951,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>45825.61666666667</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>45825.61944444444</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -2227,10 +2228,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>45825.67986111111</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>45825.70763888889</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -2504,10 +2505,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>45825.69722222222</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>45825.71111111111</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -2789,10 +2790,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>45992.55694444444</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>45992.57152777778</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -3074,10 +3075,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>45992.57638888889</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>45992.58263888889</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -3355,10 +3356,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>45992.55277777778</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>45992.59027777778</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -3632,10 +3633,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>45992.67916666667</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>45992.68402777778</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -3922,10 +3923,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>45992.67638888889</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>45992.68958333333</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -4207,10 +4208,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>45993.65</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>45993.65347222222</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -4496,10 +4497,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>45992.68055555555</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>45994.66527777778</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -4781,10 +4782,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>45994.40833333333</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>45995.28680555556</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -5054,10 +5055,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>45996.41597222222</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>45996.42638888889</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -5335,10 +5336,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>45999.54861111111</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>45999.55486111111</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -5608,10 +5609,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>45999.55763888889</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>45999.56319444445</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -5889,10 +5890,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>45999.67291666667</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>45999.67638888889</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -6170,10 +6171,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>45999.67361111111</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>45999.67986111111</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -6455,10 +6456,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>45999.67361111111</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>45999.68194444444</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -6736,10 +6737,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>45999.67152777778</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>45999.6875</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -7021,10 +7022,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>45999.71388888889</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>45999.73055555556</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -7294,10 +7295,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="6" t="n">
         <v>46000.67152777778</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>46000.67430555556</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -7571,10 +7572,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="6" t="n">
         <v>46000.68472222222</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>46000.69930555556</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -7856,10 +7857,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="6" t="n">
         <v>46001.31875</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>46001.32708333333</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -8129,10 +8130,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="6" t="n">
         <v>46002.51736111111</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>46002.52708333333</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -8410,10 +8411,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="6" t="n">
         <v>46006.85069444445</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>46006.8875</v>
       </c>
       <c r="C27" t="inlineStr">
